--- a/data/stats/supp_tables/spweedcountsPERENN-till-estimates.xlsx
+++ b/data/stats/supp_tables/spweedcountsPERENN-till-estimates.xlsx
@@ -403,19 +403,19 @@
         </is>
       </c>
       <c r="C2">
-        <v>0.1254402724938178</v>
+        <v>0.1254402713379876</v>
       </c>
       <c r="D2">
-        <v>0.1125004455687253</v>
+        <v>0.1125002694766155</v>
       </c>
       <c r="E2">
-        <v>354</v>
+        <v>17.59004012517211</v>
       </c>
       <c r="F2">
-        <v>-0.07542242200129723</v>
+        <v>-0.0880659437662715</v>
       </c>
       <c r="G2">
-        <v>0.3699399997268141</v>
+        <v>0.3889335480905529</v>
       </c>
     </row>
     <row r="3">
@@ -430,19 +430,19 @@
         </is>
       </c>
       <c r="C3">
-        <v>2.341745161461945</v>
+        <v>2.341745158029914</v>
       </c>
       <c r="D3">
-        <v>0.3340451100149299</v>
+        <v>0.3340445871372417</v>
       </c>
       <c r="E3">
-        <v>354</v>
+        <v>17.59004012517295</v>
       </c>
       <c r="F3">
-        <v>1.745327960254183</v>
+        <v>1.707785827886435</v>
       </c>
       <c r="G3">
-        <v>3.067732848617592</v>
+        <v>3.12412997594166</v>
       </c>
     </row>
     <row r="4">
@@ -457,19 +457,19 @@
         </is>
       </c>
       <c r="C4">
-        <v>1.016137317702885</v>
+        <v>1.016137315632301</v>
       </c>
       <c r="D4">
-        <v>0.2015356586346368</v>
+        <v>0.2015353431732193</v>
       </c>
       <c r="E4">
-        <v>354</v>
+        <v>17.59004012517434</v>
       </c>
       <c r="F4">
-        <v>0.6563076723601069</v>
+        <v>0.6336578021887778</v>
       </c>
       <c r="G4">
-        <v>1.454139259067854</v>
+        <v>1.488164700122016</v>
       </c>
     </row>
   </sheetData>
